--- a/data_cleaned/merged_macro_fx_dataset_2006_2024.xlsx
+++ b/data_cleaned/merged_macro_fx_dataset_2006_2024.xlsx
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>148.975</v>
       </c>
       <c r="D40" t="n">
         <v>46.83909090909</v>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>148.83</v>
       </c>
       <c r="D41" t="n">
         <v>50.84523809524</v>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>148.685</v>
       </c>
       <c r="D42" t="n">
         <v>57.94095238095</v>
